--- a/Glicko2_Predictions.xlsx
+++ b/Glicko2_Predictions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdsak\OneDrive\Desktop\Glicko-2, Etc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDACAD8-2B01-4796-8384-22A76831B151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9BDDDA-8DBF-4334-B759-498C2F3DE94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19410" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Predictions" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="587">
   <si>
     <t>Red Fighter</t>
   </si>
@@ -217,12 +217,6 @@
   </si>
   <si>
     <t>2-2</t>
-  </si>
-  <si>
-    <t>Gable Steveson</t>
-  </si>
-  <si>
-    <t>Elisha Ellison</t>
   </si>
   <si>
     <t>Cody Garbrandt</t>
@@ -2218,7 +2212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -2553,172 +2547,172 @@
         <v>63</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>46</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K8" s="4">
-        <v>1500</v>
+        <v>1655</v>
       </c>
       <c r="L8" s="5">
-        <v>1421</v>
+        <v>1658</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N8" s="7">
-        <v>0.58538698184119409</v>
+        <v>0.50361665972664749</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>46</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="K9" s="4">
-        <v>1655</v>
+        <v>1616</v>
       </c>
       <c r="L9" s="5">
-        <v>1658</v>
+        <v>1535</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="N9" s="7">
-        <v>0.50361665972664749</v>
+        <v>0.59190926777854447</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="G10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="4">
+        <v>1671</v>
+      </c>
+      <c r="L10" s="5">
+        <v>1651</v>
+      </c>
+      <c r="M10" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="K10" s="4">
-        <v>1616</v>
-      </c>
-      <c r="L10" s="5">
-        <v>1535</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="N10" s="7">
-        <v>0.59190926777854447</v>
+        <v>0.52506393721027933</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="4">
+        <v>1635</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1623</v>
+      </c>
+      <c r="M11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="4">
-        <v>1671</v>
-      </c>
-      <c r="L11" s="5">
-        <v>1651</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="N11" s="7">
-        <v>0.52506393721027933</v>
+        <v>0.51504100667607833</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2729,84 +2723,84 @@
         <v>78</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>46</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K12" s="4">
-        <v>1635</v>
+        <v>1767</v>
       </c>
       <c r="L12" s="5">
-        <v>1623</v>
+        <v>1688</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>77</v>
       </c>
       <c r="N12" s="7">
-        <v>0.51504100667607833</v>
+        <v>0.59281444631712743</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="4">
+        <v>1610</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1572</v>
+      </c>
+      <c r="M13" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="K13" s="4">
-        <v>1767</v>
-      </c>
-      <c r="L13" s="5">
-        <v>1688</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="N13" s="7">
-        <v>0.59281444631712743</v>
+        <v>0.54529260025483939</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2817,83 +2811,39 @@
         <v>83</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="G14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="I14" s="4" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K14" s="4">
-        <v>1610</v>
+        <v>1500</v>
       </c>
       <c r="L14" s="5">
-        <v>1572</v>
+        <v>1581</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N14" s="7">
-        <v>0.54529260025483939</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K15" s="4">
-        <v>1500</v>
-      </c>
-      <c r="L15" s="5">
-        <v>1581</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="N15" s="7">
         <v>0.6018522695095434</v>
       </c>
     </row>
@@ -2917,22 +2867,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2940,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C2" s="6">
         <v>1744</v>
@@ -2952,7 +2902,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2960,7 +2910,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C3" s="6">
         <v>1702</v>
@@ -2972,7 +2922,7 @@
         <v>40</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2980,7 +2930,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C4" s="6">
         <v>1698</v>
@@ -2989,10 +2939,10 @@
         <v>110</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3000,7 +2950,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C5" s="6">
         <v>1686</v>
@@ -3012,7 +2962,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3020,7 +2970,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C6" s="6">
         <v>1676</v>
@@ -3032,7 +2982,7 @@
         <v>30</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3040,7 +2990,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C7" s="6">
         <v>1676</v>
@@ -3049,10 +2999,10 @@
         <v>126</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3060,7 +3010,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C8" s="6">
         <v>1666</v>
@@ -3069,10 +3019,10 @@
         <v>112</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3080,7 +3030,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C9" s="6">
         <v>1663</v>
@@ -3092,7 +3042,7 @@
         <v>40</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3100,7 +3050,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C10" s="6">
         <v>1646</v>
@@ -3109,10 +3059,10 @@
         <v>110</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3120,7 +3070,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C11" s="6">
         <v>1640</v>
@@ -3132,7 +3082,7 @@
         <v>51</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3140,7 +3090,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C12" s="6">
         <v>1630</v>
@@ -3149,10 +3099,10 @@
         <v>132</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3160,7 +3110,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C13" s="6">
         <v>1629</v>
@@ -3172,7 +3122,7 @@
         <v>22</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3180,7 +3130,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C14" s="6">
         <v>1616</v>
@@ -3192,7 +3142,7 @@
         <v>43</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -3200,7 +3150,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C15" s="6">
         <v>1595</v>
@@ -3212,7 +3162,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -3220,7 +3170,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C16" s="6">
         <v>1570</v>
@@ -3229,10 +3179,10 @@
         <v>114</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -3240,7 +3190,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C17" s="6">
         <v>1566</v>
@@ -3252,7 +3202,7 @@
         <v>51</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3260,7 +3210,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C18" s="6">
         <v>1547</v>
@@ -3269,10 +3219,10 @@
         <v>125</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3280,7 +3230,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C19" s="6">
         <v>1541</v>
@@ -3289,10 +3239,10 @@
         <v>132</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3300,7 +3250,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C20" s="6">
         <v>1539</v>
@@ -3312,7 +3262,7 @@
         <v>21</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3320,7 +3270,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C21" s="6">
         <v>1538</v>
@@ -3329,10 +3279,10 @@
         <v>122</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3340,7 +3290,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C22" s="6">
         <v>1534</v>
@@ -3349,10 +3299,10 @@
         <v>113</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3360,7 +3310,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C23" s="6">
         <v>1526</v>
@@ -3369,10 +3319,10 @@
         <v>134</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3380,7 +3330,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C24" s="6">
         <v>1526</v>
@@ -3392,7 +3342,7 @@
         <v>37</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -3400,7 +3350,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C25" s="6">
         <v>1513</v>
@@ -3412,7 +3362,7 @@
         <v>61</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -3420,7 +3370,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C26" s="6">
         <v>1492</v>
@@ -3429,10 +3379,10 @@
         <v>117</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3455,22 +3405,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -3478,7 +3428,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C2" s="6">
         <v>1847</v>
@@ -3487,10 +3437,10 @@
         <v>110</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3498,7 +3448,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C3" s="6">
         <v>1825</v>
@@ -3507,10 +3457,10 @@
         <v>121</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3518,7 +3468,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C4" s="6">
         <v>1823</v>
@@ -3527,10 +3477,10 @@
         <v>124</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3538,7 +3488,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C5" s="6">
         <v>1819</v>
@@ -3547,10 +3497,10 @@
         <v>122</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3558,7 +3508,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C6" s="6">
         <v>1803</v>
@@ -3567,10 +3517,10 @@
         <v>114</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3578,7 +3528,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C7" s="6">
         <v>1739</v>
@@ -3587,10 +3537,10 @@
         <v>108</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3598,7 +3548,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C8" s="6">
         <v>1731</v>
@@ -3610,7 +3560,7 @@
         <v>35</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3618,7 +3568,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C9" s="6">
         <v>1723</v>
@@ -3627,10 +3577,10 @@
         <v>114</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3638,7 +3588,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C10" s="6">
         <v>1723</v>
@@ -3647,10 +3597,10 @@
         <v>109</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3658,7 +3608,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C11" s="6">
         <v>1671</v>
@@ -3667,10 +3617,10 @@
         <v>126</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3678,7 +3628,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C12" s="6">
         <v>1659</v>
@@ -3687,10 +3637,10 @@
         <v>112</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3698,7 +3648,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C13" s="6">
         <v>1654</v>
@@ -3710,7 +3660,7 @@
         <v>60</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3718,7 +3668,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C14" s="6">
         <v>1651</v>
@@ -3727,10 +3677,10 @@
         <v>132</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -3738,7 +3688,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C15" s="6">
         <v>1646</v>
@@ -3747,10 +3697,10 @@
         <v>131</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -3758,7 +3708,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C16" s="6">
         <v>1619</v>
@@ -3767,10 +3717,10 @@
         <v>132</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -3778,7 +3728,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C17" s="6">
         <v>1612</v>
@@ -3787,10 +3737,10 @@
         <v>113</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3798,7 +3748,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C18" s="6">
         <v>1610</v>
@@ -3807,10 +3757,10 @@
         <v>134</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3818,7 +3768,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C19" s="6">
         <v>1604</v>
@@ -3827,10 +3777,10 @@
         <v>112</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3838,7 +3788,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C20" s="6">
         <v>1595</v>
@@ -3850,7 +3800,7 @@
         <v>47</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3858,7 +3808,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C21" s="6">
         <v>1569</v>
@@ -3867,10 +3817,10 @@
         <v>121</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3878,7 +3828,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C22" s="6">
         <v>1569</v>
@@ -3887,10 +3837,10 @@
         <v>139</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3898,7 +3848,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C23" s="6">
         <v>1556</v>
@@ -3907,10 +3857,10 @@
         <v>126</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3918,7 +3868,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C24" s="6">
         <v>1556</v>
@@ -3930,7 +3880,7 @@
         <v>22</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -3938,7 +3888,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C25" s="6">
         <v>1555</v>
@@ -3947,10 +3897,10 @@
         <v>179</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -3958,7 +3908,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C26" s="6">
         <v>1538</v>
@@ -3967,10 +3917,10 @@
         <v>129</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -3993,22 +3943,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -4016,7 +3966,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C2" s="6">
         <v>1830</v>
@@ -4025,10 +3975,10 @@
         <v>128</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -4036,7 +3986,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C3" s="6">
         <v>1730</v>
@@ -4045,10 +3995,10 @@
         <v>112</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -4056,7 +4006,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C4" s="6">
         <v>1716</v>
@@ -4065,10 +4015,10 @@
         <v>106</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -4076,7 +4026,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C5" s="6">
         <v>1692</v>
@@ -4088,7 +4038,7 @@
         <v>34</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4096,7 +4046,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C6" s="6">
         <v>1688</v>
@@ -4108,7 +4058,7 @@
         <v>29</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4116,7 +4066,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C7" s="6">
         <v>1680</v>
@@ -4125,10 +4075,10 @@
         <v>113</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4136,7 +4086,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C8" s="6">
         <v>1677</v>
@@ -4145,10 +4095,10 @@
         <v>120</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4156,7 +4106,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C9" s="6">
         <v>1656</v>
@@ -4168,7 +4118,7 @@
         <v>28</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4176,7 +4126,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C10" s="6">
         <v>1653</v>
@@ -4188,7 +4138,7 @@
         <v>54</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4196,7 +4146,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C11" s="6">
         <v>1641</v>
@@ -4205,10 +4155,10 @@
         <v>114</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4216,7 +4166,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C12" s="6">
         <v>1639</v>
@@ -4228,7 +4178,7 @@
         <v>45</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4236,7 +4186,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C13" s="6">
         <v>1634</v>
@@ -4245,10 +4195,10 @@
         <v>117</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4256,7 +4206,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C14" s="6">
         <v>1632</v>
@@ -4268,7 +4218,7 @@
         <v>28</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4276,7 +4226,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C15" s="6">
         <v>1631</v>
@@ -4285,10 +4235,10 @@
         <v>98</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4296,7 +4246,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C16" s="6">
         <v>1627</v>
@@ -4305,10 +4255,10 @@
         <v>112</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4316,7 +4266,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C17" s="6">
         <v>1616</v>
@@ -4325,10 +4275,10 @@
         <v>107</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4336,7 +4286,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C18" s="6">
         <v>1609</v>
@@ -4345,10 +4295,10 @@
         <v>126</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4356,7 +4306,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C19" s="6">
         <v>1607</v>
@@ -4365,10 +4315,10 @@
         <v>133</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -4376,7 +4326,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C20" s="6">
         <v>1601</v>
@@ -4388,7 +4338,7 @@
         <v>45</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -4396,7 +4346,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C21" s="6">
         <v>1600</v>
@@ -4408,7 +4358,7 @@
         <v>54</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -4416,7 +4366,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C22" s="6">
         <v>1597</v>
@@ -4425,10 +4375,10 @@
         <v>126</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4436,7 +4386,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C23" s="6">
         <v>1592</v>
@@ -4448,7 +4398,7 @@
         <v>38</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -4456,7 +4406,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C24" s="6">
         <v>1591</v>
@@ -4465,10 +4415,10 @@
         <v>111</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -4476,7 +4426,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C25" s="6">
         <v>1584</v>
@@ -4488,7 +4438,7 @@
         <v>45</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -4496,7 +4446,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C26" s="6">
         <v>1564</v>
@@ -4505,10 +4455,10 @@
         <v>147</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -4531,22 +4481,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -4554,7 +4504,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C2" s="6">
         <v>2059</v>
@@ -4563,10 +4513,10 @@
         <v>128</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -4574,7 +4524,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C3" s="6">
         <v>1920</v>
@@ -4583,10 +4533,10 @@
         <v>118</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -4594,7 +4544,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C4" s="6">
         <v>1884</v>
@@ -4603,10 +4553,10 @@
         <v>110</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -4614,7 +4564,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C5" s="6">
         <v>1883</v>
@@ -4623,10 +4573,10 @@
         <v>124</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4634,7 +4584,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C6" s="6">
         <v>1874</v>
@@ -4643,10 +4593,10 @@
         <v>119</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4654,7 +4604,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7" s="6">
         <v>1862</v>
@@ -4663,10 +4613,10 @@
         <v>107</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4674,7 +4624,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C8" s="6">
         <v>1832</v>
@@ -4686,7 +4636,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4694,7 +4644,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C9" s="6">
         <v>1794</v>
@@ -4703,10 +4653,10 @@
         <v>136</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4714,7 +4664,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C10" s="6">
         <v>1783</v>
@@ -4723,10 +4673,10 @@
         <v>110</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4734,7 +4684,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C11" s="6">
         <v>1783</v>
@@ -4746,7 +4696,7 @@
         <v>26</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4754,7 +4704,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C12" s="6">
         <v>1779</v>
@@ -4766,7 +4716,7 @@
         <v>35</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4774,7 +4724,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C13" s="6">
         <v>1725</v>
@@ -4786,7 +4736,7 @@
         <v>54</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4794,7 +4744,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C14" s="6">
         <v>1717</v>
@@ -4806,7 +4756,7 @@
         <v>45</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4814,7 +4764,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C15" s="6">
         <v>1705</v>
@@ -4823,10 +4773,10 @@
         <v>102</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4834,7 +4784,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="6">
         <v>1703</v>
@@ -4846,7 +4796,7 @@
         <v>29</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4854,7 +4804,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C17" s="6">
         <v>1698</v>
@@ -4863,10 +4813,10 @@
         <v>134</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4874,7 +4824,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C18" s="6">
         <v>1696</v>
@@ -4886,7 +4836,7 @@
         <v>18</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4894,7 +4844,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C19" s="6">
         <v>1693</v>
@@ -4906,7 +4856,7 @@
         <v>30</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -4914,7 +4864,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C20" s="6">
         <v>1684</v>
@@ -4926,7 +4876,7 @@
         <v>54</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -4934,7 +4884,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C21" s="6">
         <v>1677</v>
@@ -4943,10 +4893,10 @@
         <v>119</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -4954,7 +4904,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C22" s="6">
         <v>1676</v>
@@ -4963,10 +4913,10 @@
         <v>124</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4974,7 +4924,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C23" s="6">
         <v>1675</v>
@@ -4986,7 +4936,7 @@
         <v>38</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -4994,7 +4944,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C24" s="6">
         <v>1658</v>
@@ -5003,10 +4953,10 @@
         <v>104</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -5014,7 +4964,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C25" s="6">
         <v>1657</v>
@@ -5023,10 +4973,10 @@
         <v>107</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -5034,7 +4984,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C26" s="6">
         <v>1620</v>
@@ -5046,7 +4996,7 @@
         <v>38</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -5069,22 +5019,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -5092,7 +5042,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C2" s="6">
         <v>1874</v>
@@ -5104,7 +5054,7 @@
         <v>19</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -5112,7 +5062,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C3" s="6">
         <v>1845</v>
@@ -5121,10 +5071,10 @@
         <v>110</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5132,7 +5082,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C4" s="6">
         <v>1801</v>
@@ -5144,7 +5094,7 @@
         <v>60</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5152,7 +5102,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C5" s="6">
         <v>1790</v>
@@ -5161,10 +5111,10 @@
         <v>120</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5172,7 +5122,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C6" s="6">
         <v>1784</v>
@@ -5184,7 +5134,7 @@
         <v>27</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5192,7 +5142,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C7" s="6">
         <v>1757</v>
@@ -5201,10 +5151,10 @@
         <v>110</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5212,7 +5162,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C8" s="6">
         <v>1745</v>
@@ -5221,10 +5171,10 @@
         <v>111</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5232,7 +5182,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C9" s="6">
         <v>1729</v>
@@ -5244,7 +5194,7 @@
         <v>36</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5252,7 +5202,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C10" s="6">
         <v>1717</v>
@@ -5261,10 +5211,10 @@
         <v>113</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5272,7 +5222,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C11" s="6">
         <v>1705</v>
@@ -5281,10 +5231,10 @@
         <v>132</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5292,7 +5242,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C12" s="6">
         <v>1705</v>
@@ -5301,10 +5251,10 @@
         <v>107</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -5312,7 +5262,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C13" s="6">
         <v>1695</v>
@@ -5324,7 +5274,7 @@
         <v>29</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5332,7 +5282,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C14" s="6">
         <v>1695</v>
@@ -5341,10 +5291,10 @@
         <v>116</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -5352,7 +5302,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C15" s="6">
         <v>1694</v>
@@ -5364,7 +5314,7 @@
         <v>29</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5372,7 +5322,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C16" s="6">
         <v>1686</v>
@@ -5381,10 +5331,10 @@
         <v>103</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5392,7 +5342,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C17" s="6">
         <v>1683</v>
@@ -5401,10 +5351,10 @@
         <v>110</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5424,7 +5374,7 @@
         <v>57</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5432,7 +5382,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C19" s="6">
         <v>1668</v>
@@ -5444,7 +5394,7 @@
         <v>23</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -5452,7 +5402,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C20" s="6">
         <v>1648</v>
@@ -5461,10 +5411,10 @@
         <v>124</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -5472,7 +5422,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C21" s="6">
         <v>1641</v>
@@ -5481,10 +5431,10 @@
         <v>99</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -5492,7 +5442,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C22" s="6">
         <v>1637</v>
@@ -5501,10 +5451,10 @@
         <v>116</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -5512,7 +5462,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C23" s="6">
         <v>1622</v>
@@ -5521,10 +5471,10 @@
         <v>135</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -5532,7 +5482,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C24" s="6">
         <v>1620</v>
@@ -5544,7 +5494,7 @@
         <v>45</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -5552,7 +5502,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C25" s="6">
         <v>1602</v>
@@ -5561,10 +5511,10 @@
         <v>110</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -5572,7 +5522,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C26" s="6">
         <v>1596</v>
@@ -5581,10 +5531,10 @@
         <v>180</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -5607,22 +5557,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -5630,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C2" s="6">
         <v>1909</v>
@@ -5639,10 +5589,10 @@
         <v>121</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -5650,7 +5600,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C3" s="6">
         <v>1902</v>
@@ -5659,10 +5609,10 @@
         <v>115</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5670,7 +5620,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C4" s="6">
         <v>1854</v>
@@ -5679,10 +5629,10 @@
         <v>113</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5690,7 +5640,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C5" s="6">
         <v>1839</v>
@@ -5699,10 +5649,10 @@
         <v>103</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5710,7 +5660,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C6" s="6">
         <v>1836</v>
@@ -5719,10 +5669,10 @@
         <v>103</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5742,7 +5692,7 @@
         <v>58</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5750,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C8" s="6">
         <v>1812</v>
@@ -5759,10 +5709,10 @@
         <v>117</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5770,7 +5720,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C9" s="6">
         <v>1791</v>
@@ -5782,7 +5732,7 @@
         <v>18</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5790,7 +5740,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C10" s="6">
         <v>1779</v>
@@ -5802,7 +5752,7 @@
         <v>26</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5810,7 +5760,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C11" s="6">
         <v>1779</v>
@@ -5822,7 +5772,7 @@
         <v>40</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5830,7 +5780,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C12" s="6">
         <v>1770</v>
@@ -5839,10 +5789,10 @@
         <v>124</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -5850,7 +5800,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C13" s="6">
         <v>1768</v>
@@ -5859,10 +5809,10 @@
         <v>109</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5870,7 +5820,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C14" s="6">
         <v>1756</v>
@@ -5882,7 +5832,7 @@
         <v>16</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -5890,7 +5840,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C15" s="6">
         <v>1753</v>
@@ -5899,10 +5849,10 @@
         <v>104</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5910,7 +5860,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C16" s="6">
         <v>1738</v>
@@ -5919,10 +5869,10 @@
         <v>117</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5930,7 +5880,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C17" s="6">
         <v>1735</v>
@@ -5942,7 +5892,7 @@
         <v>36</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5950,7 +5900,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C18" s="6">
         <v>1730</v>
@@ -5959,10 +5909,10 @@
         <v>127</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5970,7 +5920,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C19" s="6">
         <v>1721</v>
@@ -5979,10 +5929,10 @@
         <v>106</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -5990,7 +5940,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C20" s="6">
         <v>1720</v>
@@ -5999,10 +5949,10 @@
         <v>137</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6010,7 +5960,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C21" s="6">
         <v>1720</v>
@@ -6022,7 +5972,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -6030,7 +5980,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C22" s="6">
         <v>1705</v>
@@ -6039,10 +5989,10 @@
         <v>107</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -6050,7 +6000,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C23" s="6">
         <v>1700</v>
@@ -6062,7 +6012,7 @@
         <v>29</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -6070,7 +6020,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C24" s="6">
         <v>1685</v>
@@ -6082,7 +6032,7 @@
         <v>59</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -6090,7 +6040,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C25" s="6">
         <v>1680</v>
@@ -6102,7 +6052,7 @@
         <v>38</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -6110,7 +6060,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C26" s="6">
         <v>1677</v>
@@ -6122,7 +6072,7 @@
         <v>45</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -6145,22 +6095,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6168,7 +6118,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C2" s="6">
         <v>2020</v>
@@ -6177,10 +6127,10 @@
         <v>111</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -6188,7 +6138,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C3" s="6">
         <v>1920</v>
@@ -6197,10 +6147,10 @@
         <v>129</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -6208,7 +6158,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C4" s="6">
         <v>1908</v>
@@ -6217,10 +6167,10 @@
         <v>113</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -6228,7 +6178,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C5" s="6">
         <v>1883</v>
@@ -6237,10 +6187,10 @@
         <v>115</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -6248,7 +6198,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C6" s="6">
         <v>1880</v>
@@ -6257,10 +6207,10 @@
         <v>124</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6268,7 +6218,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C7" s="6">
         <v>1846</v>
@@ -6277,10 +6227,10 @@
         <v>113</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6288,7 +6238,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C8" s="6">
         <v>1840</v>
@@ -6297,10 +6247,10 @@
         <v>116</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6308,7 +6258,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C9" s="6">
         <v>1814</v>
@@ -6317,10 +6267,10 @@
         <v>111</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6328,7 +6278,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C10" s="6">
         <v>1812</v>
@@ -6337,10 +6287,10 @@
         <v>118</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6348,7 +6298,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C11" s="6">
         <v>1810</v>
@@ -6357,10 +6307,10 @@
         <v>116</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -6368,7 +6318,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C12" s="6">
         <v>1795</v>
@@ -6377,10 +6327,10 @@
         <v>107</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -6388,7 +6338,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C13" s="6">
         <v>1794</v>
@@ -6397,10 +6347,10 @@
         <v>120</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -6408,7 +6358,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C14" s="6">
         <v>1786</v>
@@ -6417,10 +6367,10 @@
         <v>116</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -6428,7 +6378,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C15" s="6">
         <v>1770</v>
@@ -6437,10 +6387,10 @@
         <v>132</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -6448,7 +6398,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C16" s="6">
         <v>1769</v>
@@ -6457,10 +6407,10 @@
         <v>130</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -6468,7 +6418,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C17" s="6">
         <v>1761</v>
@@ -6477,10 +6427,10 @@
         <v>112</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -6488,7 +6438,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C18" s="6">
         <v>1757</v>
@@ -6500,7 +6450,7 @@
         <v>38</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6508,7 +6458,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C19" s="6">
         <v>1752</v>
@@ -6517,10 +6467,10 @@
         <v>105</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -6528,7 +6478,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C20" s="6">
         <v>1751</v>
@@ -6540,7 +6490,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6548,7 +6498,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C21" s="6">
         <v>1745</v>
@@ -6557,10 +6507,10 @@
         <v>120</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -6568,7 +6518,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C22" s="6">
         <v>1745</v>
@@ -6580,7 +6530,7 @@
         <v>27</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -6588,7 +6538,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C23" s="6">
         <v>1732</v>
@@ -6597,10 +6547,10 @@
         <v>107</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -6608,7 +6558,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C24" s="6">
         <v>1722</v>
@@ -6620,7 +6570,7 @@
         <v>29</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -6628,7 +6578,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C25" s="6">
         <v>1719</v>
@@ -6637,10 +6587,10 @@
         <v>115</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -6648,7 +6598,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C26" s="6">
         <v>1717</v>
@@ -6657,10 +6607,10 @@
         <v>96</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -6683,22 +6633,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6706,7 +6656,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C2" s="6">
         <v>1921</v>
@@ -6715,10 +6665,10 @@
         <v>122</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -6726,7 +6676,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C3" s="6">
         <v>1898</v>
@@ -6738,7 +6688,7 @@
         <v>34</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -6746,7 +6696,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C4" s="6">
         <v>1897</v>
@@ -6755,10 +6705,10 @@
         <v>101</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -6778,7 +6728,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -6786,7 +6736,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C6" s="6">
         <v>1854</v>
@@ -6795,10 +6745,10 @@
         <v>118</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6806,7 +6756,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C7" s="6">
         <v>1821</v>
@@ -6815,10 +6765,10 @@
         <v>107</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6826,7 +6776,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C8" s="6">
         <v>1800</v>
@@ -6835,10 +6785,10 @@
         <v>112</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6858,7 +6808,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6866,7 +6816,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C10" s="6">
         <v>1791</v>
@@ -6878,7 +6828,7 @@
         <v>36</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6886,7 +6836,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C11" s="6">
         <v>1789</v>
@@ -6895,10 +6845,10 @@
         <v>110</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -6918,7 +6868,7 @@
         <v>27</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -6926,7 +6876,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C13" s="6">
         <v>1761</v>
@@ -6935,10 +6885,10 @@
         <v>106</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -6946,7 +6896,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C14" s="6">
         <v>1747</v>
@@ -6958,7 +6908,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -6966,7 +6916,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C15" s="6">
         <v>1723</v>
@@ -6975,10 +6925,10 @@
         <v>118</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -6986,7 +6936,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C16" s="6">
         <v>1720</v>
@@ -6995,10 +6945,10 @@
         <v>113</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -7006,7 +6956,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C17" s="6">
         <v>1719</v>
@@ -7015,10 +6965,10 @@
         <v>107</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -7026,7 +6976,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C18" s="6">
         <v>1711</v>
@@ -7035,10 +6985,10 @@
         <v>126</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -7046,7 +6996,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C19" s="6">
         <v>1701</v>
@@ -7055,10 +7005,10 @@
         <v>138</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -7066,7 +7016,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C20" s="6">
         <v>1697</v>
@@ -7078,7 +7028,7 @@
         <v>54</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -7086,7 +7036,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C21" s="6">
         <v>1696</v>
@@ -7095,10 +7045,10 @@
         <v>102</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -7106,7 +7056,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C22" s="6">
         <v>1690</v>
@@ -7118,7 +7068,7 @@
         <v>29</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -7126,7 +7076,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C23" s="6">
         <v>1685</v>
@@ -7138,7 +7088,7 @@
         <v>40</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -7158,7 +7108,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -7166,7 +7116,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C25" s="6">
         <v>1681</v>
@@ -7178,7 +7128,7 @@
         <v>23</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -7186,7 +7136,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C26" s="6">
         <v>1678</v>
@@ -7195,10 +7145,10 @@
         <v>118</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -7221,22 +7171,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -7244,7 +7194,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C2" s="6">
         <v>1910</v>
@@ -7253,10 +7203,10 @@
         <v>109</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -7264,7 +7214,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C3" s="6">
         <v>1871</v>
@@ -7273,10 +7223,10 @@
         <v>108</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -7284,7 +7234,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C4" s="6">
         <v>1859</v>
@@ -7293,10 +7243,10 @@
         <v>125</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -7304,7 +7254,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C5" s="6">
         <v>1809</v>
@@ -7313,10 +7263,10 @@
         <v>114</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -7324,7 +7274,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C6" s="6">
         <v>1805</v>
@@ -7333,10 +7283,10 @@
         <v>119</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -7344,7 +7294,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C7" s="6">
         <v>1793</v>
@@ -7353,10 +7303,10 @@
         <v>115</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -7364,7 +7314,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C8" s="6">
         <v>1786</v>
@@ -7376,7 +7326,7 @@
         <v>27</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -7384,7 +7334,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C9" s="6">
         <v>1771</v>
@@ -7393,10 +7343,10 @@
         <v>119</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -7404,7 +7354,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C10" s="6">
         <v>1760</v>
@@ -7413,10 +7363,10 @@
         <v>120</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -7424,7 +7374,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C11" s="6">
         <v>1752</v>
@@ -7433,10 +7383,10 @@
         <v>109</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -7444,7 +7394,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C12" s="6">
         <v>1747</v>
@@ -7453,10 +7403,10 @@
         <v>118</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -7464,7 +7414,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C13" s="6">
         <v>1745</v>
@@ -7476,7 +7426,7 @@
         <v>40</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -7484,7 +7434,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C14" s="6">
         <v>1732</v>
@@ -7496,7 +7446,7 @@
         <v>26</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -7504,7 +7454,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C15" s="6">
         <v>1725</v>
@@ -7513,10 +7463,10 @@
         <v>118</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -7524,7 +7474,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C16" s="6">
         <v>1725</v>
@@ -7533,10 +7483,10 @@
         <v>130</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -7544,7 +7494,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C17" s="6">
         <v>1718</v>
@@ -7556,7 +7506,7 @@
         <v>35</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -7564,7 +7514,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C18" s="6">
         <v>1711</v>
@@ -7573,10 +7523,10 @@
         <v>114</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -7584,7 +7534,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C19" s="6">
         <v>1708</v>
@@ -7596,7 +7546,7 @@
         <v>29</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -7604,7 +7554,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C20" s="6">
         <v>1705</v>
@@ -7613,10 +7563,10 @@
         <v>112</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -7624,7 +7574,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C21" s="6">
         <v>1695</v>
@@ -7633,10 +7583,10 @@
         <v>112</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -7644,7 +7594,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C22" s="6">
         <v>1686</v>
@@ -7653,10 +7603,10 @@
         <v>133</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -7664,7 +7614,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C23" s="6">
         <v>1684</v>
@@ -7673,10 +7623,10 @@
         <v>132</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -7684,7 +7634,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C24" s="6">
         <v>1667</v>
@@ -7696,7 +7646,7 @@
         <v>30</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -7704,7 +7654,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C25" s="6">
         <v>1666</v>
@@ -7716,7 +7666,7 @@
         <v>38</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -7724,7 +7674,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C26" s="6">
         <v>1665</v>
@@ -7736,7 +7686,7 @@
         <v>23</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -7759,22 +7709,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -7782,7 +7732,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C2" s="6">
         <v>1886</v>
@@ -7791,10 +7741,10 @@
         <v>104</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -7802,7 +7752,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C3" s="6">
         <v>1863</v>
@@ -7811,10 +7761,10 @@
         <v>109</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -7822,7 +7772,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C4" s="6">
         <v>1843</v>
@@ -7831,10 +7781,10 @@
         <v>110</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -7842,7 +7792,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C5" s="6">
         <v>1841</v>
@@ -7851,10 +7801,10 @@
         <v>121</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -7874,7 +7824,7 @@
         <v>34</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -7882,7 +7832,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C7" s="6">
         <v>1797</v>
@@ -7891,10 +7841,10 @@
         <v>108</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -7902,7 +7852,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C8" s="6">
         <v>1767</v>
@@ -7911,10 +7861,10 @@
         <v>129</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -7934,7 +7884,7 @@
         <v>35</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -7942,7 +7892,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C10" s="6">
         <v>1746</v>
@@ -7951,10 +7901,10 @@
         <v>100</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -7962,7 +7912,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C11" s="6">
         <v>1738</v>
@@ -7971,10 +7921,10 @@
         <v>115</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -7982,7 +7932,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C12" s="6">
         <v>1737</v>
@@ -7994,7 +7944,7 @@
         <v>16</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -8002,7 +7952,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C13" s="6">
         <v>1733</v>
@@ -8014,7 +7964,7 @@
         <v>29</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -8022,7 +7972,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C14" s="6">
         <v>1729</v>
@@ -8031,10 +7981,10 @@
         <v>111</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -8042,7 +7992,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C15" s="6">
         <v>1726</v>
@@ -8051,10 +8001,10 @@
         <v>119</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -8062,7 +8012,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C16" s="6">
         <v>1724</v>
@@ -8074,7 +8024,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -8082,7 +8032,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C17" s="6">
         <v>1719</v>
@@ -8091,10 +8041,10 @@
         <v>120</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -8102,7 +8052,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C18" s="6">
         <v>1709</v>
@@ -8111,10 +8061,10 @@
         <v>103</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -8122,7 +8072,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C19" s="6">
         <v>1704</v>
@@ -8134,7 +8084,7 @@
         <v>40</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -8142,7 +8092,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C20" s="6">
         <v>1700</v>
@@ -8154,7 +8104,7 @@
         <v>29</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -8162,7 +8112,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C21" s="6">
         <v>1697</v>
@@ -8171,10 +8121,10 @@
         <v>137</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -8182,7 +8132,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C22" s="6">
         <v>1694</v>
@@ -8194,7 +8144,7 @@
         <v>27</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -8202,7 +8152,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C23" s="6">
         <v>1688</v>
@@ -8214,7 +8164,7 @@
         <v>22</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -8222,7 +8172,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C24" s="6">
         <v>1685</v>
@@ -8234,7 +8184,7 @@
         <v>57</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -8242,7 +8192,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C25" s="6">
         <v>1683</v>
@@ -8254,7 +8204,7 @@
         <v>40</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -8262,7 +8212,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C26" s="6">
         <v>1682</v>
@@ -8271,10 +8221,10 @@
         <v>108</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -8297,22 +8247,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -8320,7 +8270,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C2" s="6">
         <v>1795</v>
@@ -8329,10 +8279,10 @@
         <v>111</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -8340,7 +8290,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C3" s="6">
         <v>1783</v>
@@ -8349,10 +8299,10 @@
         <v>128</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -8360,7 +8310,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C4" s="6">
         <v>1782</v>
@@ -8369,10 +8319,10 @@
         <v>117</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -8380,7 +8330,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C5" s="6">
         <v>1779</v>
@@ -8389,10 +8339,10 @@
         <v>110</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -8400,7 +8350,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C6" s="6">
         <v>1775</v>
@@ -8412,7 +8362,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -8420,7 +8370,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C7" s="6">
         <v>1735</v>
@@ -8432,7 +8382,7 @@
         <v>27</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -8440,7 +8390,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C8" s="6">
         <v>1728</v>
@@ -8449,10 +8399,10 @@
         <v>135</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -8460,7 +8410,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C9" s="6">
         <v>1717</v>
@@ -8469,10 +8419,10 @@
         <v>106</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -8480,7 +8430,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C10" s="6">
         <v>1654</v>
@@ -8492,7 +8442,7 @@
         <v>28</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -8500,7 +8450,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C11" s="6">
         <v>1651</v>
@@ -8512,7 +8462,7 @@
         <v>54</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -8520,7 +8470,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C12" s="6">
         <v>1646</v>
@@ -8529,10 +8479,10 @@
         <v>128</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -8540,7 +8490,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C13" s="6">
         <v>1646</v>
@@ -8549,10 +8499,10 @@
         <v>117</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -8560,7 +8510,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C14" s="6">
         <v>1644</v>
@@ -8572,7 +8522,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -8580,7 +8530,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C15" s="6">
         <v>1644</v>
@@ -8592,7 +8542,7 @@
         <v>22</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -8612,7 +8562,7 @@
         <v>38</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -8632,7 +8582,7 @@
         <v>43</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -8640,7 +8590,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C18" s="6">
         <v>1634</v>
@@ -8652,7 +8602,7 @@
         <v>59</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -8660,7 +8610,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C19" s="6">
         <v>1629</v>
@@ -8672,7 +8622,7 @@
         <v>38</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -8680,7 +8630,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C20" s="6">
         <v>1628</v>
@@ -8692,7 +8642,7 @@
         <v>22</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -8700,7 +8650,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C21" s="6">
         <v>1627</v>
@@ -8712,7 +8662,7 @@
         <v>28</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -8720,7 +8670,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C22" s="6">
         <v>1623</v>
@@ -8729,10 +8679,10 @@
         <v>138</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -8740,7 +8690,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C23" s="6">
         <v>1621</v>
@@ -8752,7 +8702,7 @@
         <v>22</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -8760,7 +8710,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C24" s="6">
         <v>1613</v>
@@ -8769,10 +8719,10 @@
         <v>141</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -8780,7 +8730,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C25" s="6">
         <v>1608</v>
@@ -8792,7 +8742,7 @@
         <v>47</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -8800,7 +8750,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C26" s="6">
         <v>1585</v>
@@ -8809,10 +8759,10 @@
         <v>120</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
